--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124266676</v>
+        <v>124265806</v>
       </c>
       <c r="B3" t="n">
         <v>95705</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582335</v>
+        <v>582567</v>
       </c>
       <c r="R3" t="n">
-        <v>6379312</v>
+        <v>6379248</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124264999</v>
+        <v>124265456</v>
       </c>
       <c r="B4" t="n">
         <v>57666</v>
@@ -936,7 +936,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -948,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582387</v>
+        <v>582544</v>
       </c>
       <c r="R4" t="n">
-        <v>6379276</v>
+        <v>6379245</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265895</v>
+        <v>124265556</v>
       </c>
       <c r="B5" t="n">
         <v>95705</v>
@@ -1060,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582563</v>
+        <v>582536</v>
       </c>
       <c r="R5" t="n">
-        <v>6379274</v>
+        <v>6379231</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1095,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124266581</v>
+        <v>124265895</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,39 +1152,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582359</v>
+        <v>582563</v>
       </c>
       <c r="R6" t="n">
-        <v>6379350</v>
+        <v>6379274</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1212,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,7 +1248,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124265556</v>
+        <v>124266676</v>
       </c>
       <c r="B7" t="n">
         <v>95705</v>
@@ -1289,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582536</v>
+        <v>582335</v>
       </c>
       <c r="R7" t="n">
-        <v>6379231</v>
+        <v>6379312</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1324,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124265456</v>
+        <v>124266581</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,35 +1372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1410,13 +1405,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582544</v>
+        <v>582359</v>
       </c>
       <c r="R8" t="n">
-        <v>6379245</v>
+        <v>6379350</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124265806</v>
+        <v>124264999</v>
       </c>
       <c r="B9" t="n">
-        <v>95705</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,41 +1489,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582567</v>
+        <v>582387</v>
       </c>
       <c r="R9" t="n">
-        <v>6379248</v>
+        <v>6379276</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265806</v>
+        <v>124266676</v>
       </c>
       <c r="B3" t="n">
         <v>95705</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582567</v>
+        <v>582335</v>
       </c>
       <c r="R3" t="n">
-        <v>6379248</v>
+        <v>6379312</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265556</v>
+        <v>124265895</v>
       </c>
       <c r="B5" t="n">
         <v>95705</v>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582536</v>
+        <v>582563</v>
       </c>
       <c r="R5" t="n">
-        <v>6379231</v>
+        <v>6379274</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265895</v>
+        <v>124266469</v>
       </c>
       <c r="B6" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,21 +1152,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582563</v>
+        <v>582361</v>
       </c>
       <c r="R6" t="n">
-        <v>6379274</v>
+        <v>6379359</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1248,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124266676</v>
+        <v>124265806</v>
       </c>
       <c r="B7" t="n">
         <v>95705</v>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582335</v>
+        <v>582567</v>
       </c>
       <c r="R7" t="n">
-        <v>6379312</v>
+        <v>6379248</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124266581</v>
+        <v>124265556</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,39 +1376,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582359</v>
+        <v>582536</v>
       </c>
       <c r="R8" t="n">
-        <v>6379350</v>
+        <v>6379231</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1440,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124264999</v>
+        <v>124266581</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,31 +1484,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1522,13 +1517,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582387</v>
+        <v>582359</v>
       </c>
       <c r="R9" t="n">
-        <v>6379276</v>
+        <v>6379350</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124266469</v>
+        <v>124264999</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,41 +1601,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582361</v>
+        <v>582387</v>
       </c>
       <c r="R10" t="n">
-        <v>6379359</v>
+        <v>6379276</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265456</v>
+        <v>124265895</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>95705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,50 +915,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582544</v>
+        <v>582563</v>
       </c>
       <c r="R4" t="n">
-        <v>6379245</v>
+        <v>6379274</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265895</v>
+        <v>124265556</v>
       </c>
       <c r="B5" t="n">
         <v>95705</v>
@@ -1064,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582563</v>
+        <v>582536</v>
       </c>
       <c r="R5" t="n">
-        <v>6379274</v>
+        <v>6379231</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1099,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1248,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124265806</v>
+        <v>124264999</v>
       </c>
       <c r="B7" t="n">
-        <v>95705</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,41 +1251,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582567</v>
+        <v>582387</v>
       </c>
       <c r="R7" t="n">
-        <v>6379248</v>
+        <v>6379276</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124265556</v>
+        <v>124265456</v>
       </c>
       <c r="B8" t="n">
-        <v>95705</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,41 +1368,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582536</v>
+        <v>582544</v>
       </c>
       <c r="R8" t="n">
-        <v>6379231</v>
+        <v>6379245</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1589,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124264999</v>
+        <v>124265806</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>95705</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,46 +1606,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582387</v>
+        <v>582567</v>
       </c>
       <c r="R10" t="n">
-        <v>6379276</v>
+        <v>6379248</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124266676</v>
+        <v>124265806</v>
       </c>
       <c r="B3" t="n">
         <v>95705</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582335</v>
+        <v>582567</v>
       </c>
       <c r="R3" t="n">
-        <v>6379312</v>
+        <v>6379248</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265895</v>
+        <v>124265456</v>
       </c>
       <c r="B4" t="n">
-        <v>95705</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,41 +915,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582563</v>
+        <v>582544</v>
       </c>
       <c r="R4" t="n">
-        <v>6379274</v>
+        <v>6379245</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265556</v>
+        <v>124264999</v>
       </c>
       <c r="B5" t="n">
-        <v>95705</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,41 +1036,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582536</v>
+        <v>582387</v>
       </c>
       <c r="R5" t="n">
-        <v>6379231</v>
+        <v>6379276</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124266469</v>
+        <v>124265895</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1157,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582361</v>
+        <v>582563</v>
       </c>
       <c r="R6" t="n">
-        <v>6379359</v>
+        <v>6379274</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1202,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124264999</v>
+        <v>124266581</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,31 +1265,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,13 +1298,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582387</v>
+        <v>582359</v>
       </c>
       <c r="R7" t="n">
-        <v>6379276</v>
+        <v>6379350</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124265456</v>
+        <v>124266676</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>95705</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,50 +1382,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582544</v>
+        <v>582335</v>
       </c>
       <c r="R8" t="n">
-        <v>6379245</v>
+        <v>6379312</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124266581</v>
+        <v>124265556</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,39 +1498,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582359</v>
+        <v>582536</v>
       </c>
       <c r="R9" t="n">
-        <v>6379350</v>
+        <v>6379231</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124265806</v>
+        <v>124266469</v>
       </c>
       <c r="B10" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,21 +1610,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582567</v>
+        <v>582361</v>
       </c>
       <c r="R10" t="n">
-        <v>6379248</v>
+        <v>6379359</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124264999</v>
+        <v>124265895</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>95705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,46 +1036,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582387</v>
+        <v>582563</v>
       </c>
       <c r="R5" t="n">
-        <v>6379276</v>
+        <v>6379274</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265895</v>
+        <v>124264999</v>
       </c>
       <c r="B6" t="n">
-        <v>95705</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,41 +1148,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582563</v>
+        <v>582387</v>
       </c>
       <c r="R6" t="n">
-        <v>6379274</v>
+        <v>6379276</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265456</v>
+        <v>124264999</v>
       </c>
       <c r="B4" t="n">
         <v>57666</v>
@@ -936,11 +936,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -952,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582544</v>
+        <v>582387</v>
       </c>
       <c r="R4" t="n">
-        <v>6379245</v>
+        <v>6379276</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265895</v>
+        <v>124265556</v>
       </c>
       <c r="B5" t="n">
         <v>95705</v>
@@ -1064,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582563</v>
+        <v>582536</v>
       </c>
       <c r="R5" t="n">
-        <v>6379274</v>
+        <v>6379231</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1099,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124264999</v>
+        <v>124266676</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>95705</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,46 +1144,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582387</v>
+        <v>582335</v>
       </c>
       <c r="R6" t="n">
-        <v>6379276</v>
+        <v>6379312</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124266581</v>
+        <v>124265895</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,39 +1260,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582359</v>
+        <v>582563</v>
       </c>
       <c r="R7" t="n">
-        <v>6379350</v>
+        <v>6379274</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1333,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124266676</v>
+        <v>124266469</v>
       </c>
       <c r="B8" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1410,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582335</v>
+        <v>582361</v>
       </c>
       <c r="R8" t="n">
-        <v>6379312</v>
+        <v>6379359</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1445,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124265556</v>
+        <v>124266581</v>
       </c>
       <c r="B9" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,34 +1484,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582536</v>
+        <v>582359</v>
       </c>
       <c r="R9" t="n">
-        <v>6379231</v>
+        <v>6379350</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1557,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124266469</v>
+        <v>124265456</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,41 +1597,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582361</v>
+        <v>582544</v>
       </c>
       <c r="R10" t="n">
-        <v>6379359</v>
+        <v>6379245</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -1468,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124266581</v>
+        <v>124265456</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,31 +1480,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1513,13 +1517,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582359</v>
+        <v>582544</v>
       </c>
       <c r="R9" t="n">
-        <v>6379350</v>
+        <v>6379245</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124265456</v>
+        <v>124266581</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,35 +1601,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1634,13 +1634,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582544</v>
+        <v>582359</v>
       </c>
       <c r="R10" t="n">
-        <v>6379245</v>
+        <v>6379350</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265806</v>
+        <v>124265895</v>
       </c>
       <c r="B3" t="n">
         <v>95705</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582567</v>
+        <v>582563</v>
       </c>
       <c r="R3" t="n">
-        <v>6379248</v>
+        <v>6379274</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124264999</v>
+        <v>124266469</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,46 +915,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582387</v>
+        <v>582361</v>
       </c>
       <c r="R4" t="n">
-        <v>6379276</v>
+        <v>6379359</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265556</v>
+        <v>124266581</v>
       </c>
       <c r="B5" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1031,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582536</v>
+        <v>582359</v>
       </c>
       <c r="R5" t="n">
-        <v>6379231</v>
+        <v>6379350</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124266676</v>
+        <v>124265806</v>
       </c>
       <c r="B6" t="n">
         <v>95705</v>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582335</v>
+        <v>582567</v>
       </c>
       <c r="R6" t="n">
-        <v>6379312</v>
+        <v>6379248</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124265895</v>
+        <v>124266676</v>
       </c>
       <c r="B7" t="n">
         <v>95705</v>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582563</v>
+        <v>582335</v>
       </c>
       <c r="R7" t="n">
-        <v>6379274</v>
+        <v>6379312</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124266469</v>
+        <v>124265456</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,41 +1368,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582361</v>
+        <v>582544</v>
       </c>
       <c r="R8" t="n">
-        <v>6379359</v>
+        <v>6379245</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124265456</v>
+        <v>124265556</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>95705</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,50 +1489,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582544</v>
+        <v>582536</v>
       </c>
       <c r="R9" t="n">
-        <v>6379245</v>
+        <v>6379231</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124266581</v>
+        <v>124264999</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,31 +1601,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1634,13 +1634,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582359</v>
+        <v>582387</v>
       </c>
       <c r="R10" t="n">
-        <v>6379350</v>
+        <v>6379276</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265895</v>
+        <v>124266676</v>
       </c>
       <c r="B3" t="n">
         <v>95705</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582563</v>
+        <v>582335</v>
       </c>
       <c r="R3" t="n">
-        <v>6379274</v>
+        <v>6379312</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124266469</v>
+        <v>124265806</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582361</v>
+        <v>582567</v>
       </c>
       <c r="R4" t="n">
-        <v>6379359</v>
+        <v>6379248</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124266581</v>
+        <v>124265895</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,39 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582359</v>
+        <v>582563</v>
       </c>
       <c r="R5" t="n">
-        <v>6379350</v>
+        <v>6379274</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1095,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265806</v>
+        <v>124266581</v>
       </c>
       <c r="B6" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,34 +1143,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582567</v>
+        <v>582359</v>
       </c>
       <c r="R6" t="n">
-        <v>6379248</v>
+        <v>6379350</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124266676</v>
+        <v>124266469</v>
       </c>
       <c r="B7" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582335</v>
+        <v>582361</v>
       </c>
       <c r="R7" t="n">
-        <v>6379312</v>
+        <v>6379359</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,7 +1356,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124265456</v>
+        <v>124264999</v>
       </c>
       <c r="B8" t="n">
         <v>57666</v>
@@ -1389,11 +1389,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -1405,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582544</v>
+        <v>582387</v>
       </c>
       <c r="R8" t="n">
-        <v>6379245</v>
+        <v>6379276</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1589,7 +1585,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124264999</v>
+        <v>124265456</v>
       </c>
       <c r="B10" t="n">
         <v>57666</v>
@@ -1622,7 +1618,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582387</v>
+        <v>582544</v>
       </c>
       <c r="R10" t="n">
-        <v>6379276</v>
+        <v>6379245</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265806</v>
+        <v>124265895</v>
       </c>
       <c r="B4" t="n">
         <v>95705</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582567</v>
+        <v>582563</v>
       </c>
       <c r="R4" t="n">
-        <v>6379248</v>
+        <v>6379274</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265895</v>
+        <v>124265806</v>
       </c>
       <c r="B5" t="n">
         <v>95705</v>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582563</v>
+        <v>582567</v>
       </c>
       <c r="R5" t="n">
-        <v>6379274</v>
+        <v>6379248</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124266676</v>
+        <v>124265456</v>
       </c>
       <c r="B3" t="n">
-        <v>95705</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,41 +803,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582335</v>
+        <v>582544</v>
       </c>
       <c r="R3" t="n">
-        <v>6379312</v>
+        <v>6379245</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265895</v>
+        <v>124265806</v>
       </c>
       <c r="B4" t="n">
         <v>95705</v>
@@ -943,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582563</v>
+        <v>582567</v>
       </c>
       <c r="R4" t="n">
-        <v>6379274</v>
+        <v>6379248</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -978,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265806</v>
+        <v>124265895</v>
       </c>
       <c r="B5" t="n">
         <v>95705</v>
@@ -1055,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582567</v>
+        <v>582563</v>
       </c>
       <c r="R5" t="n">
-        <v>6379248</v>
+        <v>6379274</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1090,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124266581</v>
+        <v>124265556</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,39 +1152,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582359</v>
+        <v>582536</v>
       </c>
       <c r="R6" t="n">
-        <v>6379350</v>
+        <v>6379231</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1207,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,7 +1248,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124266469</v>
+        <v>124266581</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1278,16 +1282,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582361</v>
+        <v>582359</v>
       </c>
       <c r="R7" t="n">
-        <v>6379359</v>
+        <v>6379350</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1319,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1473,7 +1482,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124265556</v>
+        <v>124266676</v>
       </c>
       <c r="B9" t="n">
         <v>95705</v>
@@ -1513,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582536</v>
+        <v>582335</v>
       </c>
       <c r="R9" t="n">
-        <v>6379231</v>
+        <v>6379312</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1548,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124265456</v>
+        <v>124266469</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,50 +1606,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582544</v>
+        <v>582361</v>
       </c>
       <c r="R10" t="n">
-        <v>6379245</v>
+        <v>6379359</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265456</v>
+        <v>124265556</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>95705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,50 +803,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582544</v>
+        <v>582536</v>
       </c>
       <c r="R3" t="n">
-        <v>6379245</v>
+        <v>6379231</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -912,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124265806</v>
+        <v>124266676</v>
       </c>
       <c r="B4" t="n">
         <v>95705</v>
@@ -952,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582567</v>
+        <v>582335</v>
       </c>
       <c r="R4" t="n">
-        <v>6379248</v>
+        <v>6379312</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -987,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265895</v>
+        <v>124265456</v>
       </c>
       <c r="B5" t="n">
-        <v>95705</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,41 +1027,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582563</v>
+        <v>582544</v>
       </c>
       <c r="R5" t="n">
-        <v>6379274</v>
+        <v>6379245</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1136,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265556</v>
+        <v>124265806</v>
       </c>
       <c r="B6" t="n">
         <v>95705</v>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582536</v>
+        <v>582567</v>
       </c>
       <c r="R6" t="n">
-        <v>6379231</v>
+        <v>6379248</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124264999</v>
+        <v>124266469</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,46 +1377,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582387</v>
+        <v>582361</v>
       </c>
       <c r="R8" t="n">
-        <v>6379276</v>
+        <v>6379359</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,7 +1477,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124266676</v>
+        <v>124265895</v>
       </c>
       <c r="B9" t="n">
         <v>95705</v>
@@ -1522,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582335</v>
+        <v>582563</v>
       </c>
       <c r="R9" t="n">
-        <v>6379312</v>
+        <v>6379274</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1557,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124266469</v>
+        <v>124264999</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,41 +1601,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582361</v>
+        <v>582387</v>
       </c>
       <c r="R10" t="n">
-        <v>6379359</v>
+        <v>6379276</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124265556</v>
+        <v>124266469</v>
       </c>
       <c r="B3" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582536</v>
+        <v>582361</v>
       </c>
       <c r="R3" t="n">
-        <v>6379231</v>
+        <v>6379359</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124266676</v>
+        <v>124264999</v>
       </c>
       <c r="B4" t="n">
-        <v>95705</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,41 +915,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582335</v>
+        <v>582387</v>
       </c>
       <c r="R4" t="n">
-        <v>6379312</v>
+        <v>6379276</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1136,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124265806</v>
+        <v>124266581</v>
       </c>
       <c r="B6" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,34 +1157,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582567</v>
+        <v>582359</v>
       </c>
       <c r="R6" t="n">
-        <v>6379248</v>
+        <v>6379350</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1211,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124266581</v>
+        <v>124265895</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,39 +1274,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582359</v>
+        <v>582563</v>
       </c>
       <c r="R7" t="n">
-        <v>6379350</v>
+        <v>6379274</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1328,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124266469</v>
+        <v>124265556</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1386,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582361</v>
+        <v>582536</v>
       </c>
       <c r="R8" t="n">
-        <v>6379359</v>
+        <v>6379231</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1440,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,7 +1482,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124265895</v>
+        <v>124265806</v>
       </c>
       <c r="B9" t="n">
         <v>95705</v>
@@ -1517,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582563</v>
+        <v>582567</v>
       </c>
       <c r="R9" t="n">
-        <v>6379274</v>
+        <v>6379248</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1552,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124264999</v>
+        <v>124266676</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>95705</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,46 +1606,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582387</v>
+        <v>582335</v>
       </c>
       <c r="R10" t="n">
-        <v>6379276</v>
+        <v>6379312</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 17954-2025 artfynd.xlsx
+++ b/artfynd/A 17954-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124266469</v>
+        <v>124266581</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -825,16 +825,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582361</v>
+        <v>582359</v>
       </c>
       <c r="R3" t="n">
-        <v>6379359</v>
+        <v>6379350</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -866,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124264999</v>
+        <v>124265556</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>95705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,46 +920,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582387</v>
+        <v>582536</v>
       </c>
       <c r="R4" t="n">
-        <v>6379276</v>
+        <v>6379231</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124265456</v>
+        <v>124266469</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,50 +1032,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582544</v>
+        <v>582361</v>
       </c>
       <c r="R5" t="n">
-        <v>6379245</v>
+        <v>6379359</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124266581</v>
+        <v>124264999</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,31 +1144,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1186,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582359</v>
+        <v>582387</v>
       </c>
       <c r="R6" t="n">
-        <v>6379350</v>
+        <v>6379276</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1249,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124265895</v>
+        <v>124265806</v>
       </c>
       <c r="B7" t="n">
         <v>95705</v>
@@ -1298,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582563</v>
+        <v>582567</v>
       </c>
       <c r="R7" t="n">
-        <v>6379274</v>
+        <v>6379248</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1333,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124265556</v>
+        <v>124265895</v>
       </c>
       <c r="B8" t="n">
         <v>95705</v>
@@ -1410,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582536</v>
+        <v>582563</v>
       </c>
       <c r="R8" t="n">
-        <v>6379231</v>
+        <v>6379274</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1445,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124265806</v>
+        <v>124265456</v>
       </c>
       <c r="B9" t="n">
-        <v>95705</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,41 +1485,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupbäckskärret, Djupbäckskärret, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582567</v>
+        <v>582544</v>
       </c>
       <c r="R9" t="n">
-        <v>6379248</v>
+        <v>6379245</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
